--- a/manifests/dataset_manifest.xlsx
+++ b/manifests/dataset_manifest.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q200"/>
+  <dimension ref="A1:S200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,8 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -586,6 +588,16 @@
           <t>비고(수정 내용)</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>출처 데이터셋</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>원래 split</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2"/>
@@ -605,6 +617,8 @@
       <c r="O2" s="10"/>
       <c r="P2" s="11"/>
       <c r="Q2" s="3"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2"/>
@@ -624,6 +638,8 @@
       <c r="O3" s="10"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="3"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2"/>
@@ -643,6 +659,8 @@
       <c r="O4" s="10"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="3"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2"/>
@@ -662,6 +680,8 @@
       <c r="O5" s="10"/>
       <c r="P5" s="11"/>
       <c r="Q5" s="3"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2"/>
@@ -681,6 +701,8 @@
       <c r="O6" s="10"/>
       <c r="P6" s="11"/>
       <c r="Q6" s="3"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2"/>
@@ -700,6 +722,8 @@
       <c r="O7" s="10"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="3"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2"/>
@@ -719,6 +743,8 @@
       <c r="O8" s="10"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="3"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2"/>
@@ -738,6 +764,8 @@
       <c r="O9" s="10"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="3"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2"/>
@@ -757,6 +785,8 @@
       <c r="O10" s="10"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="3"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2"/>
@@ -776,6 +806,8 @@
       <c r="O11" s="10"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="3"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2"/>
@@ -795,6 +827,8 @@
       <c r="O12" s="10"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="3"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2"/>
@@ -814,6 +848,8 @@
       <c r="O13" s="10"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="3"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2"/>
@@ -833,6 +869,8 @@
       <c r="O14" s="10"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="3"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2"/>
@@ -852,6 +890,8 @@
       <c r="O15" s="10"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="3"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2"/>
@@ -871,6 +911,8 @@
       <c r="O16" s="10"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="3"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="2"/>
@@ -890,6 +932,8 @@
       <c r="O17" s="10"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="3"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="2"/>
@@ -909,6 +953,8 @@
       <c r="O18" s="10"/>
       <c r="P18" s="11"/>
       <c r="Q18" s="3"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="2"/>
@@ -928,6 +974,8 @@
       <c r="O19" s="10"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="3"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="2"/>
@@ -947,6 +995,8 @@
       <c r="O20" s="10"/>
       <c r="P20" s="11"/>
       <c r="Q20" s="3"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="2"/>
@@ -966,6 +1016,8 @@
       <c r="O21" s="10"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="3"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" s="2"/>
@@ -985,6 +1037,8 @@
       <c r="O22" s="10"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="3"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="2"/>
@@ -1004,6 +1058,8 @@
       <c r="O23" s="10"/>
       <c r="P23" s="11"/>
       <c r="Q23" s="3"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2"/>
@@ -1023,6 +1079,8 @@
       <c r="O24" s="10"/>
       <c r="P24" s="11"/>
       <c r="Q24" s="3"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" s="2"/>
@@ -1042,6 +1100,8 @@
       <c r="O25" s="10"/>
       <c r="P25" s="11"/>
       <c r="Q25" s="3"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" s="2"/>
@@ -1061,6 +1121,8 @@
       <c r="O26" s="10"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="3"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="2"/>
@@ -1080,6 +1142,8 @@
       <c r="O27" s="10"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="3"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="2"/>
@@ -1099,6 +1163,8 @@
       <c r="O28" s="10"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="3"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" s="2"/>
@@ -1118,6 +1184,8 @@
       <c r="O29" s="10"/>
       <c r="P29" s="11"/>
       <c r="Q29" s="3"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" s="2"/>
@@ -1137,6 +1205,8 @@
       <c r="O30" s="10"/>
       <c r="P30" s="11"/>
       <c r="Q30" s="3"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" s="2"/>
@@ -1156,6 +1226,8 @@
       <c r="O31" s="10"/>
       <c r="P31" s="11"/>
       <c r="Q31" s="3"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" s="2"/>
@@ -1175,6 +1247,8 @@
       <c r="O32" s="10"/>
       <c r="P32" s="11"/>
       <c r="Q32" s="3"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" s="2"/>
@@ -1194,6 +1268,8 @@
       <c r="O33" s="10"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="3"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" s="2"/>
@@ -1213,6 +1289,8 @@
       <c r="O34" s="10"/>
       <c r="P34" s="11"/>
       <c r="Q34" s="3"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" s="2"/>
@@ -1232,6 +1310,8 @@
       <c r="O35" s="10"/>
       <c r="P35" s="11"/>
       <c r="Q35" s="3"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" s="2"/>
@@ -1251,6 +1331,8 @@
       <c r="O36" s="10"/>
       <c r="P36" s="11"/>
       <c r="Q36" s="3"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" s="2"/>
@@ -1270,6 +1352,8 @@
       <c r="O37" s="10"/>
       <c r="P37" s="11"/>
       <c r="Q37" s="3"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" s="2"/>
@@ -1289,6 +1373,8 @@
       <c r="O38" s="10"/>
       <c r="P38" s="11"/>
       <c r="Q38" s="3"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" s="2"/>
@@ -1308,6 +1394,8 @@
       <c r="O39" s="10"/>
       <c r="P39" s="11"/>
       <c r="Q39" s="3"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" s="2"/>
@@ -1327,6 +1415,8 @@
       <c r="O40" s="10"/>
       <c r="P40" s="11"/>
       <c r="Q40" s="3"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" s="2"/>
@@ -1346,6 +1436,8 @@
       <c r="O41" s="10"/>
       <c r="P41" s="11"/>
       <c r="Q41" s="3"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" s="2"/>
@@ -1365,6 +1457,8 @@
       <c r="O42" s="10"/>
       <c r="P42" s="11"/>
       <c r="Q42" s="3"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" s="2"/>
@@ -1384,6 +1478,8 @@
       <c r="O43" s="10"/>
       <c r="P43" s="11"/>
       <c r="Q43" s="3"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" s="2"/>
@@ -1403,6 +1499,8 @@
       <c r="O44" s="10"/>
       <c r="P44" s="11"/>
       <c r="Q44" s="3"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" s="2"/>
@@ -1422,6 +1520,8 @@
       <c r="O45" s="10"/>
       <c r="P45" s="11"/>
       <c r="Q45" s="3"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" s="2"/>
@@ -1441,6 +1541,8 @@
       <c r="O46" s="10"/>
       <c r="P46" s="11"/>
       <c r="Q46" s="3"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" s="2"/>
@@ -1460,6 +1562,8 @@
       <c r="O47" s="10"/>
       <c r="P47" s="11"/>
       <c r="Q47" s="3"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" s="2"/>
@@ -1479,6 +1583,8 @@
       <c r="O48" s="10"/>
       <c r="P48" s="11"/>
       <c r="Q48" s="3"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" s="2"/>
@@ -1498,6 +1604,8 @@
       <c r="O49" s="10"/>
       <c r="P49" s="11"/>
       <c r="Q49" s="3"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" s="2"/>
@@ -1517,6 +1625,8 @@
       <c r="O50" s="10"/>
       <c r="P50" s="11"/>
       <c r="Q50" s="3"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" s="2"/>
@@ -1536,6 +1646,8 @@
       <c r="O51" s="10"/>
       <c r="P51" s="11"/>
       <c r="Q51" s="3"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" s="2"/>
@@ -1555,6 +1667,8 @@
       <c r="O52" s="10"/>
       <c r="P52" s="11"/>
       <c r="Q52" s="3"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" s="2"/>
@@ -1574,6 +1688,8 @@
       <c r="O53" s="10"/>
       <c r="P53" s="11"/>
       <c r="Q53" s="3"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" s="2"/>
@@ -1593,6 +1709,8 @@
       <c r="O54" s="10"/>
       <c r="P54" s="11"/>
       <c r="Q54" s="3"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" s="2"/>
@@ -1612,6 +1730,8 @@
       <c r="O55" s="10"/>
       <c r="P55" s="11"/>
       <c r="Q55" s="3"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" s="2"/>
@@ -1631,6 +1751,8 @@
       <c r="O56" s="10"/>
       <c r="P56" s="11"/>
       <c r="Q56" s="3"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="2"/>
@@ -1650,6 +1772,8 @@
       <c r="O57" s="10"/>
       <c r="P57" s="11"/>
       <c r="Q57" s="3"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" s="2"/>
@@ -1669,6 +1793,8 @@
       <c r="O58" s="10"/>
       <c r="P58" s="11"/>
       <c r="Q58" s="3"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" s="2"/>
@@ -1688,6 +1814,8 @@
       <c r="O59" s="10"/>
       <c r="P59" s="11"/>
       <c r="Q59" s="3"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" s="2"/>
@@ -1707,6 +1835,8 @@
       <c r="O60" s="10"/>
       <c r="P60" s="11"/>
       <c r="Q60" s="3"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" s="2"/>
@@ -1726,6 +1856,8 @@
       <c r="O61" s="10"/>
       <c r="P61" s="11"/>
       <c r="Q61" s="3"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" s="2"/>
@@ -1745,6 +1877,8 @@
       <c r="O62" s="10"/>
       <c r="P62" s="11"/>
       <c r="Q62" s="3"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" s="2"/>
@@ -1764,6 +1898,8 @@
       <c r="O63" s="10"/>
       <c r="P63" s="11"/>
       <c r="Q63" s="3"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" s="2"/>
@@ -1783,6 +1919,8 @@
       <c r="O64" s="10"/>
       <c r="P64" s="11"/>
       <c r="Q64" s="3"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" s="2"/>
@@ -1802,6 +1940,8 @@
       <c r="O65" s="10"/>
       <c r="P65" s="11"/>
       <c r="Q65" s="3"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" s="2"/>
@@ -1821,6 +1961,8 @@
       <c r="O66" s="10"/>
       <c r="P66" s="11"/>
       <c r="Q66" s="3"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" s="2"/>
@@ -1840,6 +1982,8 @@
       <c r="O67" s="10"/>
       <c r="P67" s="11"/>
       <c r="Q67" s="3"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" s="2"/>
@@ -1859,6 +2003,8 @@
       <c r="O68" s="10"/>
       <c r="P68" s="11"/>
       <c r="Q68" s="3"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" s="2"/>
@@ -1878,6 +2024,8 @@
       <c r="O69" s="10"/>
       <c r="P69" s="11"/>
       <c r="Q69" s="3"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="2"/>
@@ -1897,6 +2045,8 @@
       <c r="O70" s="10"/>
       <c r="P70" s="11"/>
       <c r="Q70" s="3"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="2"/>
@@ -1916,6 +2066,8 @@
       <c r="O71" s="10"/>
       <c r="P71" s="11"/>
       <c r="Q71" s="3"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" s="2"/>
@@ -1935,6 +2087,8 @@
       <c r="O72" s="10"/>
       <c r="P72" s="11"/>
       <c r="Q72" s="3"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" s="2"/>
@@ -1954,6 +2108,8 @@
       <c r="O73" s="10"/>
       <c r="P73" s="11"/>
       <c r="Q73" s="3"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" s="2"/>
@@ -1973,6 +2129,8 @@
       <c r="O74" s="10"/>
       <c r="P74" s="11"/>
       <c r="Q74" s="3"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" s="2"/>
@@ -1992,6 +2150,8 @@
       <c r="O75" s="10"/>
       <c r="P75" s="11"/>
       <c r="Q75" s="3"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" s="2"/>
@@ -2011,6 +2171,8 @@
       <c r="O76" s="10"/>
       <c r="P76" s="11"/>
       <c r="Q76" s="3"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" s="2"/>
@@ -2030,6 +2192,8 @@
       <c r="O77" s="10"/>
       <c r="P77" s="11"/>
       <c r="Q77" s="3"/>
+      <c r="R77" s="2"/>
+      <c r="S77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" s="2"/>
@@ -2049,6 +2213,8 @@
       <c r="O78" s="10"/>
       <c r="P78" s="11"/>
       <c r="Q78" s="3"/>
+      <c r="R78" s="2"/>
+      <c r="S78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" s="2"/>
@@ -2068,6 +2234,8 @@
       <c r="O79" s="10"/>
       <c r="P79" s="11"/>
       <c r="Q79" s="3"/>
+      <c r="R79" s="2"/>
+      <c r="S79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" s="2"/>
@@ -2087,6 +2255,8 @@
       <c r="O80" s="10"/>
       <c r="P80" s="11"/>
       <c r="Q80" s="3"/>
+      <c r="R80" s="2"/>
+      <c r="S80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" s="2"/>
@@ -2106,6 +2276,8 @@
       <c r="O81" s="10"/>
       <c r="P81" s="11"/>
       <c r="Q81" s="3"/>
+      <c r="R81" s="2"/>
+      <c r="S81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" s="2"/>
@@ -2125,6 +2297,8 @@
       <c r="O82" s="10"/>
       <c r="P82" s="11"/>
       <c r="Q82" s="3"/>
+      <c r="R82" s="2"/>
+      <c r="S82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" s="2"/>
@@ -2144,6 +2318,8 @@
       <c r="O83" s="10"/>
       <c r="P83" s="11"/>
       <c r="Q83" s="3"/>
+      <c r="R83" s="2"/>
+      <c r="S83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" s="2"/>
@@ -2163,6 +2339,8 @@
       <c r="O84" s="10"/>
       <c r="P84" s="11"/>
       <c r="Q84" s="3"/>
+      <c r="R84" s="2"/>
+      <c r="S84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" s="2"/>
@@ -2182,6 +2360,8 @@
       <c r="O85" s="10"/>
       <c r="P85" s="11"/>
       <c r="Q85" s="3"/>
+      <c r="R85" s="2"/>
+      <c r="S85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" s="2"/>
@@ -2201,6 +2381,8 @@
       <c r="O86" s="10"/>
       <c r="P86" s="11"/>
       <c r="Q86" s="3"/>
+      <c r="R86" s="2"/>
+      <c r="S86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" s="2"/>
@@ -2220,6 +2402,8 @@
       <c r="O87" s="10"/>
       <c r="P87" s="11"/>
       <c r="Q87" s="3"/>
+      <c r="R87" s="2"/>
+      <c r="S87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" s="2"/>
@@ -2239,6 +2423,8 @@
       <c r="O88" s="10"/>
       <c r="P88" s="11"/>
       <c r="Q88" s="3"/>
+      <c r="R88" s="2"/>
+      <c r="S88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" s="2"/>
@@ -2258,6 +2444,8 @@
       <c r="O89" s="10"/>
       <c r="P89" s="11"/>
       <c r="Q89" s="3"/>
+      <c r="R89" s="2"/>
+      <c r="S89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" s="2"/>
@@ -2277,6 +2465,8 @@
       <c r="O90" s="10"/>
       <c r="P90" s="11"/>
       <c r="Q90" s="3"/>
+      <c r="R90" s="2"/>
+      <c r="S90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" s="2"/>
@@ -2296,6 +2486,8 @@
       <c r="O91" s="10"/>
       <c r="P91" s="11"/>
       <c r="Q91" s="3"/>
+      <c r="R91" s="2"/>
+      <c r="S91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" s="2"/>
@@ -2315,6 +2507,8 @@
       <c r="O92" s="10"/>
       <c r="P92" s="11"/>
       <c r="Q92" s="3"/>
+      <c r="R92" s="2"/>
+      <c r="S92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" s="2"/>
@@ -2334,6 +2528,8 @@
       <c r="O93" s="10"/>
       <c r="P93" s="11"/>
       <c r="Q93" s="3"/>
+      <c r="R93" s="2"/>
+      <c r="S93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" s="2"/>
@@ -2353,6 +2549,8 @@
       <c r="O94" s="10"/>
       <c r="P94" s="11"/>
       <c r="Q94" s="3"/>
+      <c r="R94" s="2"/>
+      <c r="S94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" s="2"/>
@@ -2372,6 +2570,8 @@
       <c r="O95" s="10"/>
       <c r="P95" s="11"/>
       <c r="Q95" s="3"/>
+      <c r="R95" s="2"/>
+      <c r="S95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" s="2"/>
@@ -2391,6 +2591,8 @@
       <c r="O96" s="10"/>
       <c r="P96" s="11"/>
       <c r="Q96" s="3"/>
+      <c r="R96" s="2"/>
+      <c r="S96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" s="2"/>
@@ -2410,6 +2612,8 @@
       <c r="O97" s="10"/>
       <c r="P97" s="11"/>
       <c r="Q97" s="3"/>
+      <c r="R97" s="2"/>
+      <c r="S97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" s="2"/>
@@ -2429,6 +2633,8 @@
       <c r="O98" s="10"/>
       <c r="P98" s="11"/>
       <c r="Q98" s="3"/>
+      <c r="R98" s="2"/>
+      <c r="S98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" s="2"/>
@@ -2448,6 +2654,8 @@
       <c r="O99" s="10"/>
       <c r="P99" s="11"/>
       <c r="Q99" s="3"/>
+      <c r="R99" s="2"/>
+      <c r="S99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" s="2"/>
@@ -2467,6 +2675,8 @@
       <c r="O100" s="10"/>
       <c r="P100" s="11"/>
       <c r="Q100" s="3"/>
+      <c r="R100" s="2"/>
+      <c r="S100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" s="2"/>
@@ -2486,6 +2696,8 @@
       <c r="O101" s="10"/>
       <c r="P101" s="11"/>
       <c r="Q101" s="3"/>
+      <c r="R101" s="2"/>
+      <c r="S101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" s="2"/>
@@ -2505,6 +2717,8 @@
       <c r="O102" s="10"/>
       <c r="P102" s="11"/>
       <c r="Q102" s="3"/>
+      <c r="R102" s="2"/>
+      <c r="S102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" s="2"/>
@@ -2524,6 +2738,8 @@
       <c r="O103" s="10"/>
       <c r="P103" s="11"/>
       <c r="Q103" s="3"/>
+      <c r="R103" s="2"/>
+      <c r="S103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" s="2"/>
@@ -2543,6 +2759,8 @@
       <c r="O104" s="10"/>
       <c r="P104" s="11"/>
       <c r="Q104" s="3"/>
+      <c r="R104" s="2"/>
+      <c r="S104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" s="2"/>
@@ -2562,6 +2780,8 @@
       <c r="O105" s="10"/>
       <c r="P105" s="11"/>
       <c r="Q105" s="3"/>
+      <c r="R105" s="2"/>
+      <c r="S105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" s="2"/>
@@ -2581,6 +2801,8 @@
       <c r="O106" s="10"/>
       <c r="P106" s="11"/>
       <c r="Q106" s="3"/>
+      <c r="R106" s="2"/>
+      <c r="S106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" s="2"/>
@@ -2600,6 +2822,8 @@
       <c r="O107" s="10"/>
       <c r="P107" s="11"/>
       <c r="Q107" s="3"/>
+      <c r="R107" s="2"/>
+      <c r="S107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" s="2"/>
@@ -2619,6 +2843,8 @@
       <c r="O108" s="10"/>
       <c r="P108" s="11"/>
       <c r="Q108" s="3"/>
+      <c r="R108" s="2"/>
+      <c r="S108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" s="2"/>
@@ -2638,6 +2864,8 @@
       <c r="O109" s="10"/>
       <c r="P109" s="11"/>
       <c r="Q109" s="3"/>
+      <c r="R109" s="2"/>
+      <c r="S109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" s="2"/>
@@ -2657,6 +2885,8 @@
       <c r="O110" s="10"/>
       <c r="P110" s="11"/>
       <c r="Q110" s="3"/>
+      <c r="R110" s="2"/>
+      <c r="S110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" s="2"/>
@@ -2676,6 +2906,8 @@
       <c r="O111" s="10"/>
       <c r="P111" s="11"/>
       <c r="Q111" s="3"/>
+      <c r="R111" s="2"/>
+      <c r="S111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" s="2"/>
@@ -2695,6 +2927,8 @@
       <c r="O112" s="10"/>
       <c r="P112" s="11"/>
       <c r="Q112" s="3"/>
+      <c r="R112" s="2"/>
+      <c r="S112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" s="2"/>
@@ -2714,6 +2948,8 @@
       <c r="O113" s="10"/>
       <c r="P113" s="11"/>
       <c r="Q113" s="3"/>
+      <c r="R113" s="2"/>
+      <c r="S113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" s="2"/>
@@ -2733,6 +2969,8 @@
       <c r="O114" s="10"/>
       <c r="P114" s="11"/>
       <c r="Q114" s="3"/>
+      <c r="R114" s="2"/>
+      <c r="S114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" s="2"/>
@@ -2752,6 +2990,8 @@
       <c r="O115" s="10"/>
       <c r="P115" s="11"/>
       <c r="Q115" s="3"/>
+      <c r="R115" s="2"/>
+      <c r="S115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" s="2"/>
@@ -2771,6 +3011,8 @@
       <c r="O116" s="10"/>
       <c r="P116" s="11"/>
       <c r="Q116" s="3"/>
+      <c r="R116" s="2"/>
+      <c r="S116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" s="2"/>
@@ -2790,6 +3032,8 @@
       <c r="O117" s="10"/>
       <c r="P117" s="11"/>
       <c r="Q117" s="3"/>
+      <c r="R117" s="2"/>
+      <c r="S117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" s="2"/>
@@ -2809,6 +3053,8 @@
       <c r="O118" s="10"/>
       <c r="P118" s="11"/>
       <c r="Q118" s="3"/>
+      <c r="R118" s="2"/>
+      <c r="S118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" s="2"/>
@@ -2828,6 +3074,8 @@
       <c r="O119" s="10"/>
       <c r="P119" s="11"/>
       <c r="Q119" s="3"/>
+      <c r="R119" s="2"/>
+      <c r="S119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" s="2"/>
@@ -2847,6 +3095,8 @@
       <c r="O120" s="10"/>
       <c r="P120" s="11"/>
       <c r="Q120" s="3"/>
+      <c r="R120" s="2"/>
+      <c r="S120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" s="2"/>
@@ -2866,6 +3116,8 @@
       <c r="O121" s="10"/>
       <c r="P121" s="11"/>
       <c r="Q121" s="3"/>
+      <c r="R121" s="2"/>
+      <c r="S121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" s="2"/>
@@ -2885,6 +3137,8 @@
       <c r="O122" s="10"/>
       <c r="P122" s="11"/>
       <c r="Q122" s="3"/>
+      <c r="R122" s="2"/>
+      <c r="S122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" s="2"/>
@@ -2904,6 +3158,8 @@
       <c r="O123" s="10"/>
       <c r="P123" s="11"/>
       <c r="Q123" s="3"/>
+      <c r="R123" s="2"/>
+      <c r="S123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" s="2"/>
@@ -2923,6 +3179,8 @@
       <c r="O124" s="10"/>
       <c r="P124" s="11"/>
       <c r="Q124" s="3"/>
+      <c r="R124" s="2"/>
+      <c r="S124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" s="2"/>
@@ -2942,6 +3200,8 @@
       <c r="O125" s="10"/>
       <c r="P125" s="11"/>
       <c r="Q125" s="3"/>
+      <c r="R125" s="2"/>
+      <c r="S125" s="2"/>
     </row>
     <row r="126">
       <c r="A126" s="2"/>
@@ -2961,6 +3221,8 @@
       <c r="O126" s="10"/>
       <c r="P126" s="11"/>
       <c r="Q126" s="3"/>
+      <c r="R126" s="2"/>
+      <c r="S126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" s="2"/>
@@ -2980,6 +3242,8 @@
       <c r="O127" s="10"/>
       <c r="P127" s="11"/>
       <c r="Q127" s="3"/>
+      <c r="R127" s="2"/>
+      <c r="S127" s="2"/>
     </row>
     <row r="128">
       <c r="A128" s="2"/>
@@ -2999,6 +3263,8 @@
       <c r="O128" s="10"/>
       <c r="P128" s="11"/>
       <c r="Q128" s="3"/>
+      <c r="R128" s="2"/>
+      <c r="S128" s="2"/>
     </row>
     <row r="129">
       <c r="A129" s="2"/>
@@ -3018,6 +3284,8 @@
       <c r="O129" s="10"/>
       <c r="P129" s="11"/>
       <c r="Q129" s="3"/>
+      <c r="R129" s="2"/>
+      <c r="S129" s="2"/>
     </row>
     <row r="130">
       <c r="A130" s="2"/>
@@ -3037,6 +3305,8 @@
       <c r="O130" s="10"/>
       <c r="P130" s="11"/>
       <c r="Q130" s="3"/>
+      <c r="R130" s="2"/>
+      <c r="S130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" s="2"/>
@@ -3056,6 +3326,8 @@
       <c r="O131" s="10"/>
       <c r="P131" s="11"/>
       <c r="Q131" s="3"/>
+      <c r="R131" s="2"/>
+      <c r="S131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" s="2"/>
@@ -3075,6 +3347,8 @@
       <c r="O132" s="10"/>
       <c r="P132" s="11"/>
       <c r="Q132" s="3"/>
+      <c r="R132" s="2"/>
+      <c r="S132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" s="2"/>
@@ -3094,6 +3368,8 @@
       <c r="O133" s="10"/>
       <c r="P133" s="11"/>
       <c r="Q133" s="3"/>
+      <c r="R133" s="2"/>
+      <c r="S133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" s="2"/>
@@ -3113,6 +3389,8 @@
       <c r="O134" s="10"/>
       <c r="P134" s="11"/>
       <c r="Q134" s="3"/>
+      <c r="R134" s="2"/>
+      <c r="S134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" s="2"/>
@@ -3132,6 +3410,8 @@
       <c r="O135" s="10"/>
       <c r="P135" s="11"/>
       <c r="Q135" s="3"/>
+      <c r="R135" s="2"/>
+      <c r="S135" s="2"/>
     </row>
     <row r="136">
       <c r="A136" s="2"/>
@@ -3151,6 +3431,8 @@
       <c r="O136" s="10"/>
       <c r="P136" s="11"/>
       <c r="Q136" s="3"/>
+      <c r="R136" s="2"/>
+      <c r="S136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" s="2"/>
@@ -3170,6 +3452,8 @@
       <c r="O137" s="10"/>
       <c r="P137" s="11"/>
       <c r="Q137" s="3"/>
+      <c r="R137" s="2"/>
+      <c r="S137" s="2"/>
     </row>
     <row r="138">
       <c r="A138" s="2"/>
@@ -3189,6 +3473,8 @@
       <c r="O138" s="10"/>
       <c r="P138" s="11"/>
       <c r="Q138" s="3"/>
+      <c r="R138" s="2"/>
+      <c r="S138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" s="2"/>
@@ -3208,6 +3494,8 @@
       <c r="O139" s="10"/>
       <c r="P139" s="11"/>
       <c r="Q139" s="3"/>
+      <c r="R139" s="2"/>
+      <c r="S139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" s="2"/>
@@ -3227,6 +3515,8 @@
       <c r="O140" s="10"/>
       <c r="P140" s="11"/>
       <c r="Q140" s="3"/>
+      <c r="R140" s="2"/>
+      <c r="S140" s="2"/>
     </row>
     <row r="141">
       <c r="A141" s="2"/>
@@ -3246,6 +3536,8 @@
       <c r="O141" s="10"/>
       <c r="P141" s="11"/>
       <c r="Q141" s="3"/>
+      <c r="R141" s="2"/>
+      <c r="S141" s="2"/>
     </row>
     <row r="142">
       <c r="A142" s="2"/>
@@ -3265,6 +3557,8 @@
       <c r="O142" s="10"/>
       <c r="P142" s="11"/>
       <c r="Q142" s="3"/>
+      <c r="R142" s="2"/>
+      <c r="S142" s="2"/>
     </row>
     <row r="143">
       <c r="A143" s="2"/>
@@ -3284,6 +3578,8 @@
       <c r="O143" s="10"/>
       <c r="P143" s="11"/>
       <c r="Q143" s="3"/>
+      <c r="R143" s="2"/>
+      <c r="S143" s="2"/>
     </row>
     <row r="144">
       <c r="A144" s="2"/>
@@ -3303,6 +3599,8 @@
       <c r="O144" s="10"/>
       <c r="P144" s="11"/>
       <c r="Q144" s="3"/>
+      <c r="R144" s="2"/>
+      <c r="S144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" s="2"/>
@@ -3322,6 +3620,8 @@
       <c r="O145" s="10"/>
       <c r="P145" s="11"/>
       <c r="Q145" s="3"/>
+      <c r="R145" s="2"/>
+      <c r="S145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" s="2"/>
@@ -3341,6 +3641,8 @@
       <c r="O146" s="10"/>
       <c r="P146" s="11"/>
       <c r="Q146" s="3"/>
+      <c r="R146" s="2"/>
+      <c r="S146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" s="2"/>
@@ -3360,6 +3662,8 @@
       <c r="O147" s="10"/>
       <c r="P147" s="11"/>
       <c r="Q147" s="3"/>
+      <c r="R147" s="2"/>
+      <c r="S147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" s="2"/>
@@ -3379,6 +3683,8 @@
       <c r="O148" s="10"/>
       <c r="P148" s="11"/>
       <c r="Q148" s="3"/>
+      <c r="R148" s="2"/>
+      <c r="S148" s="2"/>
     </row>
     <row r="149">
       <c r="A149" s="2"/>
@@ -3398,6 +3704,8 @@
       <c r="O149" s="10"/>
       <c r="P149" s="11"/>
       <c r="Q149" s="3"/>
+      <c r="R149" s="2"/>
+      <c r="S149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" s="2"/>
@@ -3417,6 +3725,8 @@
       <c r="O150" s="10"/>
       <c r="P150" s="11"/>
       <c r="Q150" s="3"/>
+      <c r="R150" s="2"/>
+      <c r="S150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" s="2"/>
@@ -3436,6 +3746,8 @@
       <c r="O151" s="10"/>
       <c r="P151" s="11"/>
       <c r="Q151" s="3"/>
+      <c r="R151" s="2"/>
+      <c r="S151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" s="2"/>
@@ -3455,6 +3767,8 @@
       <c r="O152" s="10"/>
       <c r="P152" s="11"/>
       <c r="Q152" s="3"/>
+      <c r="R152" s="2"/>
+      <c r="S152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" s="2"/>
@@ -3474,6 +3788,8 @@
       <c r="O153" s="10"/>
       <c r="P153" s="11"/>
       <c r="Q153" s="3"/>
+      <c r="R153" s="2"/>
+      <c r="S153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" s="2"/>
@@ -3493,6 +3809,8 @@
       <c r="O154" s="10"/>
       <c r="P154" s="11"/>
       <c r="Q154" s="3"/>
+      <c r="R154" s="2"/>
+      <c r="S154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" s="2"/>
@@ -3512,6 +3830,8 @@
       <c r="O155" s="10"/>
       <c r="P155" s="11"/>
       <c r="Q155" s="3"/>
+      <c r="R155" s="2"/>
+      <c r="S155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" s="2"/>
@@ -3531,6 +3851,8 @@
       <c r="O156" s="10"/>
       <c r="P156" s="11"/>
       <c r="Q156" s="3"/>
+      <c r="R156" s="2"/>
+      <c r="S156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" s="2"/>
@@ -3550,6 +3872,8 @@
       <c r="O157" s="10"/>
       <c r="P157" s="11"/>
       <c r="Q157" s="3"/>
+      <c r="R157" s="2"/>
+      <c r="S157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" s="2"/>
@@ -3569,6 +3893,8 @@
       <c r="O158" s="10"/>
       <c r="P158" s="11"/>
       <c r="Q158" s="3"/>
+      <c r="R158" s="2"/>
+      <c r="S158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" s="2"/>
@@ -3588,6 +3914,8 @@
       <c r="O159" s="10"/>
       <c r="P159" s="11"/>
       <c r="Q159" s="3"/>
+      <c r="R159" s="2"/>
+      <c r="S159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" s="2"/>
@@ -3607,6 +3935,8 @@
       <c r="O160" s="10"/>
       <c r="P160" s="11"/>
       <c r="Q160" s="3"/>
+      <c r="R160" s="2"/>
+      <c r="S160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" s="2"/>
@@ -3626,6 +3956,8 @@
       <c r="O161" s="10"/>
       <c r="P161" s="11"/>
       <c r="Q161" s="3"/>
+      <c r="R161" s="2"/>
+      <c r="S161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" s="2"/>
@@ -3645,6 +3977,8 @@
       <c r="O162" s="10"/>
       <c r="P162" s="11"/>
       <c r="Q162" s="3"/>
+      <c r="R162" s="2"/>
+      <c r="S162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" s="2"/>
@@ -3664,6 +3998,8 @@
       <c r="O163" s="10"/>
       <c r="P163" s="11"/>
       <c r="Q163" s="3"/>
+      <c r="R163" s="2"/>
+      <c r="S163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" s="2"/>
@@ -3683,6 +4019,8 @@
       <c r="O164" s="10"/>
       <c r="P164" s="11"/>
       <c r="Q164" s="3"/>
+      <c r="R164" s="2"/>
+      <c r="S164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" s="2"/>
@@ -3702,6 +4040,8 @@
       <c r="O165" s="10"/>
       <c r="P165" s="11"/>
       <c r="Q165" s="3"/>
+      <c r="R165" s="2"/>
+      <c r="S165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" s="2"/>
@@ -3721,6 +4061,8 @@
       <c r="O166" s="10"/>
       <c r="P166" s="11"/>
       <c r="Q166" s="3"/>
+      <c r="R166" s="2"/>
+      <c r="S166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" s="2"/>
@@ -3740,6 +4082,8 @@
       <c r="O167" s="10"/>
       <c r="P167" s="11"/>
       <c r="Q167" s="3"/>
+      <c r="R167" s="2"/>
+      <c r="S167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" s="2"/>
@@ -3759,6 +4103,8 @@
       <c r="O168" s="10"/>
       <c r="P168" s="11"/>
       <c r="Q168" s="3"/>
+      <c r="R168" s="2"/>
+      <c r="S168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" s="2"/>
@@ -3778,6 +4124,8 @@
       <c r="O169" s="10"/>
       <c r="P169" s="11"/>
       <c r="Q169" s="3"/>
+      <c r="R169" s="2"/>
+      <c r="S169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" s="2"/>
@@ -3797,6 +4145,8 @@
       <c r="O170" s="10"/>
       <c r="P170" s="11"/>
       <c r="Q170" s="3"/>
+      <c r="R170" s="2"/>
+      <c r="S170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" s="2"/>
@@ -3816,6 +4166,8 @@
       <c r="O171" s="10"/>
       <c r="P171" s="11"/>
       <c r="Q171" s="3"/>
+      <c r="R171" s="2"/>
+      <c r="S171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" s="2"/>
@@ -3835,6 +4187,8 @@
       <c r="O172" s="10"/>
       <c r="P172" s="11"/>
       <c r="Q172" s="3"/>
+      <c r="R172" s="2"/>
+      <c r="S172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" s="2"/>
@@ -3854,6 +4208,8 @@
       <c r="O173" s="10"/>
       <c r="P173" s="11"/>
       <c r="Q173" s="3"/>
+      <c r="R173" s="2"/>
+      <c r="S173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" s="2"/>
@@ -3873,6 +4229,8 @@
       <c r="O174" s="10"/>
       <c r="P174" s="11"/>
       <c r="Q174" s="3"/>
+      <c r="R174" s="2"/>
+      <c r="S174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" s="2"/>
@@ -3892,6 +4250,8 @@
       <c r="O175" s="10"/>
       <c r="P175" s="11"/>
       <c r="Q175" s="3"/>
+      <c r="R175" s="2"/>
+      <c r="S175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" s="2"/>
@@ -3911,6 +4271,8 @@
       <c r="O176" s="10"/>
       <c r="P176" s="11"/>
       <c r="Q176" s="3"/>
+      <c r="R176" s="2"/>
+      <c r="S176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" s="2"/>
@@ -3930,6 +4292,8 @@
       <c r="O177" s="10"/>
       <c r="P177" s="11"/>
       <c r="Q177" s="3"/>
+      <c r="R177" s="2"/>
+      <c r="S177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" s="2"/>
@@ -3949,6 +4313,8 @@
       <c r="O178" s="10"/>
       <c r="P178" s="11"/>
       <c r="Q178" s="3"/>
+      <c r="R178" s="2"/>
+      <c r="S178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" s="2"/>
@@ -3968,6 +4334,8 @@
       <c r="O179" s="10"/>
       <c r="P179" s="11"/>
       <c r="Q179" s="3"/>
+      <c r="R179" s="2"/>
+      <c r="S179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" s="2"/>
@@ -3987,6 +4355,8 @@
       <c r="O180" s="10"/>
       <c r="P180" s="11"/>
       <c r="Q180" s="3"/>
+      <c r="R180" s="2"/>
+      <c r="S180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" s="2"/>
@@ -4006,6 +4376,8 @@
       <c r="O181" s="10"/>
       <c r="P181" s="11"/>
       <c r="Q181" s="3"/>
+      <c r="R181" s="2"/>
+      <c r="S181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" s="2"/>
@@ -4025,6 +4397,8 @@
       <c r="O182" s="10"/>
       <c r="P182" s="11"/>
       <c r="Q182" s="3"/>
+      <c r="R182" s="2"/>
+      <c r="S182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" s="2"/>
@@ -4044,6 +4418,8 @@
       <c r="O183" s="10"/>
       <c r="P183" s="11"/>
       <c r="Q183" s="3"/>
+      <c r="R183" s="2"/>
+      <c r="S183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" s="2"/>
@@ -4063,6 +4439,8 @@
       <c r="O184" s="10"/>
       <c r="P184" s="11"/>
       <c r="Q184" s="3"/>
+      <c r="R184" s="2"/>
+      <c r="S184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" s="2"/>
@@ -4082,6 +4460,8 @@
       <c r="O185" s="10"/>
       <c r="P185" s="11"/>
       <c r="Q185" s="3"/>
+      <c r="R185" s="2"/>
+      <c r="S185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" s="2"/>
@@ -4101,6 +4481,8 @@
       <c r="O186" s="10"/>
       <c r="P186" s="11"/>
       <c r="Q186" s="3"/>
+      <c r="R186" s="2"/>
+      <c r="S186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" s="2"/>
@@ -4120,6 +4502,8 @@
       <c r="O187" s="10"/>
       <c r="P187" s="11"/>
       <c r="Q187" s="3"/>
+      <c r="R187" s="2"/>
+      <c r="S187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" s="2"/>
@@ -4139,6 +4523,8 @@
       <c r="O188" s="10"/>
       <c r="P188" s="11"/>
       <c r="Q188" s="3"/>
+      <c r="R188" s="2"/>
+      <c r="S188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" s="2"/>
@@ -4158,6 +4544,8 @@
       <c r="O189" s="10"/>
       <c r="P189" s="11"/>
       <c r="Q189" s="3"/>
+      <c r="R189" s="2"/>
+      <c r="S189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" s="2"/>
@@ -4177,6 +4565,8 @@
       <c r="O190" s="10"/>
       <c r="P190" s="11"/>
       <c r="Q190" s="3"/>
+      <c r="R190" s="2"/>
+      <c r="S190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" s="2"/>
@@ -4196,6 +4586,8 @@
       <c r="O191" s="10"/>
       <c r="P191" s="11"/>
       <c r="Q191" s="3"/>
+      <c r="R191" s="2"/>
+      <c r="S191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" s="2"/>
@@ -4215,6 +4607,8 @@
       <c r="O192" s="10"/>
       <c r="P192" s="11"/>
       <c r="Q192" s="3"/>
+      <c r="R192" s="2"/>
+      <c r="S192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" s="2"/>
@@ -4234,6 +4628,8 @@
       <c r="O193" s="10"/>
       <c r="P193" s="11"/>
       <c r="Q193" s="3"/>
+      <c r="R193" s="2"/>
+      <c r="S193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" s="2"/>
@@ -4253,6 +4649,8 @@
       <c r="O194" s="10"/>
       <c r="P194" s="11"/>
       <c r="Q194" s="3"/>
+      <c r="R194" s="2"/>
+      <c r="S194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" s="2"/>
@@ -4272,6 +4670,8 @@
       <c r="O195" s="10"/>
       <c r="P195" s="11"/>
       <c r="Q195" s="3"/>
+      <c r="R195" s="2"/>
+      <c r="S195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" s="2"/>
@@ -4291,6 +4691,8 @@
       <c r="O196" s="10"/>
       <c r="P196" s="11"/>
       <c r="Q196" s="3"/>
+      <c r="R196" s="2"/>
+      <c r="S196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" s="2"/>
@@ -4310,6 +4712,8 @@
       <c r="O197" s="10"/>
       <c r="P197" s="11"/>
       <c r="Q197" s="3"/>
+      <c r="R197" s="2"/>
+      <c r="S197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" s="2"/>
@@ -4329,6 +4733,8 @@
       <c r="O198" s="10"/>
       <c r="P198" s="11"/>
       <c r="Q198" s="3"/>
+      <c r="R198" s="2"/>
+      <c r="S198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" s="2"/>
@@ -4348,6 +4754,8 @@
       <c r="O199" s="10"/>
       <c r="P199" s="11"/>
       <c r="Q199" s="3"/>
+      <c r="R199" s="2"/>
+      <c r="S199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" s="2"/>
@@ -4367,11 +4775,19 @@
       <c r="O200" s="10"/>
       <c r="P200" s="11"/>
       <c r="Q200" s="3"/>
+      <c r="R200" s="2"/>
+      <c r="S200" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"검수 전,검수 완료,수정 필요,수정 완료,제외"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"이물검출_학습데이터1,이물검출_학습데이터2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"train,validation"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
